--- a/src/app/ML/models/training_report.xlsx
+++ b/src/app/ML/models/training_report.xlsx
@@ -23,7 +23,7 @@
     <t>Data/Hora</t>
   </si>
   <si>
-    <t>2025-12-02T12:42:59+00:00</t>
+    <t>2026-04-29T22:16:26+00:00</t>
   </si>
   <si>
     <t>Épocas</t>
@@ -503,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.44444444444444</v>
+        <v>0.40740740740741</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -511,7 +511,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.20277777777778</v>
+        <v>0.19705882352941</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -566,13 +566,13 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.47826086956522</v>
+        <v>0.47619047619048</v>
       </c>
       <c r="C16">
-        <v>0.84615384615385</v>
+        <v>0.76923076923077</v>
       </c>
       <c r="D16">
-        <v>0.61111111111111</v>
+        <v>0.58823529411765</v>
       </c>
       <c r="E16">
         <v>13</v>
@@ -612,8 +612,11 @@
       <c r="B22">
         <v>1</v>
       </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
       <c r="D22">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -629,21 +632,18 @@
         <v>19</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>20</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
       <c r="D25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/src/app/ML/models/training_report.xlsx
+++ b/src/app/ML/models/training_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
   <si>
     <t>Relatório de Treinamento RubixML</t>
   </si>
@@ -23,7 +23,7 @@
     <t>Data/Hora</t>
   </si>
   <si>
-    <t>2026-04-29T22:16:26+00:00</t>
+    <t>2026-04-29T22:58:32+00:00</t>
   </si>
   <si>
     <t>Épocas</t>
@@ -35,9 +35,6 @@
     <t>K-Fold</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>Métrica</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
   </si>
   <si>
     <t>Amostras</t>
-  </si>
-  <si>
-    <t>babosa_do_campo</t>
   </si>
   <si>
     <t>capivara</t>
@@ -440,14 +434,14 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="23.423" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="30.564" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="10.569" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="9.10" bestFit="true" style="0"/>
     <col min="7" max="7" width="9.10" bestFit="true" style="0"/>
     <col min="8" max="8" width="9.10" bestFit="true" style="0"/>
@@ -471,7 +465,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -479,83 +473,83 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
+      <c r="B6">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
         <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>0.40740740740741</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>0.19705882352941</v>
+        <v>0.20634920634921</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>14</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>15</v>
-      </c>
-      <c r="E13" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14">
+        <v>0.33333333333333</v>
+      </c>
+      <c r="C14">
         <v>0.25</v>
       </c>
-      <c r="C14">
-        <v>0.16666666666667</v>
-      </c>
       <c r="D14">
-        <v>0.2</v>
+        <v>0.28571428571429</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15">
         <v>4</v>
@@ -563,87 +557,68 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>0.25</v>
+      </c>
+      <c r="C16">
+        <v>0.5</v>
+      </c>
+      <c r="D16">
+        <v>0.33333333333333</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16">
-        <v>0.47619047619048</v>
-      </c>
-      <c r="C16">
-        <v>0.76923076923077</v>
-      </c>
-      <c r="D16">
-        <v>0.58823529411765</v>
-      </c>
-      <c r="E16">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="1" t="s">
-        <v>21</v>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" t="s">
-        <v>20</v>
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>17</v>
       </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
       <c r="D22">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>18</v>
       </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
       <c r="D23">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24">
-        <v>3</v>
-      </c>
-      <c r="D24">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/src/app/ML/models/training_report.xlsx
+++ b/src/app/ML/models/training_report.xlsx
@@ -23,7 +23,7 @@
     <t>Data/Hora</t>
   </si>
   <si>
-    <t>2026-04-29T22:58:32+00:00</t>
+    <t>2026-04-30T09:59:42+00:00</t>
   </si>
   <si>
     <t>Épocas</t>
@@ -497,7 +497,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.25</v>
+        <v>0.33333333333333</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -505,7 +505,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.20634920634921</v>
+        <v>0.32671957671958</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -535,13 +535,13 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>0.33333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="C14">
         <v>0.25</v>
       </c>
       <c r="D14">
-        <v>0.28571428571429</v>
+        <v>0.25</v>
       </c>
       <c r="E14">
         <v>4</v>
@@ -551,6 +551,15 @@
       <c r="A15" t="s">
         <v>17</v>
       </c>
+      <c r="B15">
+        <v>0.33333333333333</v>
+      </c>
+      <c r="C15">
+        <v>0.25</v>
+      </c>
+      <c r="D15">
+        <v>0.28571428571429</v>
+      </c>
       <c r="E15">
         <v>4</v>
       </c>
@@ -560,13 +569,13 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="C16">
         <v>0.5</v>
       </c>
       <c r="D16">
-        <v>0.33333333333333</v>
+        <v>0.44444444444444</v>
       </c>
       <c r="E16">
         <v>4</v>
@@ -596,18 +605,24 @@
         <v>1</v>
       </c>
       <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
         <v>1</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>17</v>
       </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
       <c r="D22">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:8">

--- a/src/app/ML/models/training_report.xlsx
+++ b/src/app/ML/models/training_report.xlsx
@@ -23,7 +23,7 @@
     <t>Data/Hora</t>
   </si>
   <si>
-    <t>2025-12-02T12:42:59+00:00</t>
+    <t>2026-04-23T12:41:46+00:00</t>
   </si>
   <si>
     <t>Épocas</t>
@@ -471,7 +471,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -503,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.44444444444444</v>
+        <v>0.65116279069767</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -511,7 +511,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.20277777777778</v>
+        <v>0.57453019521985</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -541,13 +541,13 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.25</v>
+        <v>0.33333333333333</v>
       </c>
       <c r="C14">
         <v>0.16666666666667</v>
       </c>
       <c r="D14">
-        <v>0.2</v>
+        <v>0.22222222222222</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -557,8 +557,17 @@
       <c r="A15" t="s">
         <v>18</v>
       </c>
+      <c r="B15">
+        <v>0.73333333333333</v>
+      </c>
+      <c r="C15">
+        <v>0.91666666666667</v>
+      </c>
+      <c r="D15">
+        <v>0.81481481481481</v>
+      </c>
       <c r="E15">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -566,13 +575,13 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.47826086956522</v>
+        <v>0.75</v>
       </c>
       <c r="C16">
-        <v>0.84615384615385</v>
+        <v>0.46153846153846</v>
       </c>
       <c r="D16">
-        <v>0.61111111111111</v>
+        <v>0.57142857142857</v>
       </c>
       <c r="E16">
         <v>13</v>
@@ -582,8 +591,17 @@
       <c r="A17" t="s">
         <v>20</v>
       </c>
+      <c r="B17">
+        <v>0.58823529411765</v>
+      </c>
+      <c r="C17">
+        <v>0.83333333333333</v>
+      </c>
+      <c r="D17">
+        <v>0.68965517241379</v>
+      </c>
       <c r="E17">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -612,16 +630,25 @@
       <c r="B22">
         <v>1</v>
       </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
       <c r="D22">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>18</v>
       </c>
+      <c r="C23">
+        <v>11</v>
+      </c>
       <c r="D23">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -632,18 +659,21 @@
         <v>2</v>
       </c>
       <c r="D24">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="E24">
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>20</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/src/app/ML/models/training_report.xlsx
+++ b/src/app/ML/models/training_report.xlsx
@@ -23,7 +23,7 @@
     <t>Data/Hora</t>
   </si>
   <si>
-    <t>2026-04-30T09:59:42+00:00</t>
+    <t>2026-05-21T14:20:29+00:00</t>
   </si>
   <si>
     <t>Épocas</t>
@@ -439,8 +439,8 @@
   <cols>
     <col min="1" max="1" width="23.423" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="30.564" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="10.569" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="9.10" bestFit="true" style="0"/>
     <col min="7" max="7" width="9.10" bestFit="true" style="0"/>
@@ -473,7 +473,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>168</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -497,7 +497,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.33333333333333</v>
+        <v>0.54761904761905</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -505,7 +505,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.32671957671958</v>
+        <v>0.53333333333333</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -535,16 +535,16 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="C14">
-        <v>0.25</v>
+        <v>0.42857142857143</v>
       </c>
       <c r="D14">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -552,16 +552,16 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>0.33333333333333</v>
+        <v>0.46153846153846</v>
       </c>
       <c r="C15">
-        <v>0.25</v>
+        <v>0.85714285714286</v>
       </c>
       <c r="D15">
-        <v>0.28571428571429</v>
+        <v>0.6</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -569,16 +569,16 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>0.4</v>
+        <v>0.83333333333333</v>
       </c>
       <c r="C16">
+        <v>0.35714285714286</v>
+      </c>
+      <c r="D16">
         <v>0.5</v>
       </c>
-      <c r="D16">
-        <v>0.44444444444444</v>
-      </c>
       <c r="E16">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -602,13 +602,10 @@
         <v>16</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -619,10 +616,10 @@
         <v>1</v>
       </c>
       <c r="C22">
+        <v>12</v>
+      </c>
+      <c r="D22">
         <v>1</v>
-      </c>
-      <c r="D22">
-        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -630,10 +627,13 @@
         <v>18</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
